--- a/01_경혈별_해부생리_분석보고서/SP_족태음비경/SP05_상구/SP05_상구_해부생리_분석데이터.xlsx
+++ b/01_경혈별_해부생리_분석보고서/SP_족태음비경/SP05_상구/SP05_상구_해부생리_분석데이터.xlsx
@@ -17,7 +17,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8.ARI_v3.0" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="9.FMA_해부실체" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10.주치분리" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="개정이력" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11.분기추론_TriTarget" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="개정이력" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -438,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -862,6 +863,422 @@
       <c r="F13" s="2" t="inlineStr">
         <is>
           <t>P_single 근거</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>证治通鉴 明堂 주치(한글번역)</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>한열이 나고 잘 구역질함… 궐두통, 얼굴이 부어오름. 비가 허하면 몸이 차고 즐겁지 않은 병… 배가 그득하여 꾸르륵거림, 대변이 순조롭지 않음…</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>중국침구증치통감(中国针灸证治通鉴)/中国针灸证治通鉴_05_第壹编_第七篇_足太阴脾经_手少阴心经_手太阳小肠经_한글번역.md</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>L157~165</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>한대</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>P_single 기술(한글 번역본 기준, 원문 L118~126과 대조 — 불일치 없음)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>证治通鉴 千金翼 상구 조문(원문·한글번역)</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>商丘，在内踝前陷中，主偏风，痹脚不得履地… / 상구는 안쪽 복사뼈 앞의 오목한 가운데에 있으며… 뜸은 꺼린다</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>중국침구증치통감(中国针灸证治通鉴)/中国针灸证治通鉴_14_第叁编_内科病症_四中风至八痉证.md ; …_한글번역.md</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>L194 ; L354</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>당</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>P_single(원문 기준·번역 기술, 불일치 없음)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>证治通鉴 神应经 身寒痹(원문·한글번역)</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>身寒痹：曲池、列缺、环跳、风市、委中、商丘、中封、临泣 / 신한비: 곡지·열결·환도·풍시·위중·상구·중봉·임읍</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>중국침구증치통감(中国针灸证治通鉴)/中国针灸证治通鉴_02_第壹编_第二至四篇_治疗原则_腧穴证治_量化概念.md ; …_한글번역.md</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>L172 ; L215</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>명</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>P_comb</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>经络通鉴 灵枢·经脉 足太阴 순행</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>脾足太阴之脉，起于大指之端，循指内侧白肉际，过核骨后，上内踝前廉</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>중국침구경락통감(中国针灸经络通鉴)/中国针灸经络通鉴_21_第叁编_第四篇_足太阴经脉、经别、络脉和经筋.md</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>L162</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>선진·한대</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>원천(경맥 순행) — 해당 혈 직접 언급 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>经络通鉴 경맥 주가(铜人·十四经发挥·医学纲目)</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>商丘居此内踝之前 / 历太白、公孙、商丘，上内踝前廉之三阴交 / 内踝下前陷中，商丘穴也</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>중국침구경락통감(中国针灸经络通鉴)/中国针灸经络通鉴_21_第叁编_第四篇_足太阴经脉、经别、络脉和经筋.md</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>L188, L199, L230</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>송~명</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>재해석(경맥 순행에 혈위 배치)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>经络通鉴 太素·本输 杨上善 주</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>［行于商丘，商丘者，内踝下陷者之中也，为经；］《明堂》足内踝下微前</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>중국침구경락통감(中国针灸经络通鉴)/中国针灸经络通鉴_21_第叁编_第四篇_足太阴经脉、经别、络脉和经筋.md</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>L306 (본수 원문 L302; 11편 L484·L488·L492 동문)</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>수당</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>本输 下 = 明堂 下微前 해석</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>经络通鉴 足太阴之筋 주</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>上结于内踝骨下之商丘(马莳) / 结于内踝下，商丘之次(张介宾) / 并足太阴商丘之次(足少阴之筋)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>중국침구경락통감(中国针灸经络通鉴)/中国针灸经络通鉴_21_第叁编_第四篇_足太阴经脉、经别、络脉和经筋.md ; 중국침구경락통감(中国针灸经络通鉴)/中国针灸经络通鉴_25_第叁编_第八篇_足少阴经脉、经别、络脉和经筋.md</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>L845, L851 ; L980</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>명</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>경근 결처 = 상구 자리</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>经络通鉴 足太阴过于外踝 필사 오류</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>足太阴过于外[1]踝之上 / [1] 外：疑为“内”字之误 / 明抄本《甲乙经》作“内踝”，《太素》同 / 惟此足太阴经，上于内踝薄肉之处，脉得见者也</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>중국침구경락통감(中国针灸经络通鉴)/中国针灸经络通鉴_21_第叁编_第四篇_足太阴经脉、经别、络脉和经筋.md</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>L69, L77, L98, L182</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>선진·한대(교감)</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>Rank 4 필사 오류(外→内) — 눈에 보이는 맥 = 큰두렁정맥(추론)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>经络通鉴 张介宾 横脉 주</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>足太阴刺其横脉出血，谓足内踝前斜过大脉，则太阴之经，盖即商丘也</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>중국침구경락통감(中国针灸经络通鉴)/中国针灸经络通鉴_20_第叁编_第三篇_足阳明经脉、经别、络脉和经筋(三).md</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>L1402</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>명</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>Layer 1 큰두렁정맥 대응(추론)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>经络通鉴 经脉穴(内经→明堂)</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>其对应关系为：足太阴——商丘、太白 / 除“足太阴”穴六朝以后变化较大外</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>중국침구경락통감(中国针灸经络通鉴)/中国针灸经络通鉴_01_第壹编_第一篇_“经脉”概念的形成与经络学说的建立.md</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>L783~785, L731</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>한대(고증)</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>通考 L1055 귀속 = 경맥혈 독해(경락론 확장 아님)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>经络通鉴 灵枢·厥病 太阴/太阳 이문</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>《灵枢》“太阴”，《甲乙》、《太素》作“太阳”，而《明堂》则取…足太阴之“公孙”、“商丘”穴，与《灵枢》相合</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>중국침구경락통감(中国针灸经络通鉴)/中国针灸经络通鉴_20_第叁编_第三篇_足阳明经脉、经别、络脉和经筋(三).md</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>L1986</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>한대(교감)</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>厥头痛·面肿 주치 귀속의 이문</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>经络通鉴 脾疟 杨上善·王冰 주</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>可取脾之经脉大都、公孙、商丘等穴 / 商丘主之。商丘在足内踝下微前陷者中</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>중국침구경락통감(中国针灸经络通鉴)/中国针灸经络通鉴_21_第叁编_第四篇_足太阴经脉、经别、络脉和经筋.md</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>L1233, L1247</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>수당</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>脾疟 조문의 혈위 지정</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>经络通鉴 脉名索引</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>◇足太阴 … 35 … (经脉穴 논의 쪽) / 商坵·商邱 표기 0건(전편 검색)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>중국침구경락통감(中国针灸经络通鉴)/中国针灸经络通鉴_37_第伍编_附篇一_脉名索引.md</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>L535</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>이명 검색 결과</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1601,261 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="48" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>구분</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>X (전후)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Y (상하)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Z / Δ(추정)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>근거·판정</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Target 1 (고전 문헌)</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>灵枢·本输 内踝之下陷者之中 (明堂 下微前, 杨上善·王冰 주)</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>안쪽복사 앞모서리 선 부근</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>안쪽복사 아래모서리 바로 아래</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>3푼 6.9mm</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>通考 L973~975; 经络通鉴 21편 L306·L1247</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Target 2 (촉진 실체화·자입 기준점)</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>陷者之中/宛宛中/陷中 = 앞정강근 힘줄(FMA:47050) 안쪽 가장자리–안쪽복사 앞아래 간극</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>힘줄 안쪽 가장자리 바로 안쪽</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>안쪽복사 아래모서리 가로선</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Layer 3 오목 결합조직</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>경계: FMA:47050, 안쪽복사, 발배뼈 거친면, FMA:44055 바닥, FMA:21376·45262 안쪽 피하</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Target 3 (WHO)</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>舟骨粗隆–内踝尖 연결선 중점 오목(국표 2006)</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>안쪽복사 앞모서리 선</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>안쪽복사 아래모서리 가로선</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>직자 5~8푼 11.5~18.4mm</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>通考 L947, L969~971</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Δ T1–T2</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr"/>
+      <c r="C5" s="2" t="inlineStr"/>
+      <c r="D5" s="2" t="inlineStr"/>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>약 0~10mm</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>병합 — 같은 오목, 안쪽복사 크기 안쪽</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Δ T1–T3</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr"/>
+      <c r="C6" s="2" t="inlineStr"/>
+      <c r="D6" s="2" t="inlineStr"/>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>약 0~10mm</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>병합(경계값 근접: 本输를 수직 아래로 읽으면 조해 쪽으로 &gt;10mm 가능하나 明堂·杨上善·王冰 주와 상충해 불채택)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Δ T2–T3</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr"/>
+      <c r="C7" s="2" t="inlineStr"/>
+      <c r="D7" s="2" t="inlineStr"/>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>약 0~5mm</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>병합</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>판정</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Target 1≡2≡3 단일 Target</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr"/>
+      <c r="D8" s="2" t="inlineStr"/>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>분기 기준 Δ &gt; 10mm</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>분기 불요; 10mm 기준으로 상태 바뀐 쌍 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>구판 대응</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>구 단일 Target(T1) → Target 1≡2≡3</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr"/>
+      <c r="D9" s="2" t="inlineStr"/>
+      <c r="E9" s="2" t="inlineStr"/>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>이중 채점 승계(위치 불변)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1272,6 +1943,33 @@
       <c r="E3" s="2" t="inlineStr">
         <is>
           <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>1·8·11 시트</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>3대 원전 스크리닝, S_orig ④ 通考 교감, 분기추론 시트 없음</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>经络通鉴 10행·证治通鉴 한글번역 3행 추가(파일·행 포인터), ④ 通考·经络通鉴 교감 재점검(75 유지), Tri-Target 좌표·Δ 시트 신설(Δ &gt; 10mm 기준, Target 1≡2≡3). 점수 불변</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Framework 2.7.7; 분기 기준 Δ &gt; 10mm(2026-10-25)</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3798,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>S_orig ④ 通考 교감</t>
+          <t>S_orig ④ 通考·经络通鉴 교감</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr"/>
@@ -3113,12 +3811,12 @@
       <c r="E5" s="2" t="inlineStr"/>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>黄疸·舌本强痛 지적, 忌灸 이문 미판정</t>
+          <t>黄疸·舌本强痛 지적, 忌灸 이문 미판정 / 2.7.7 재점검: 经络通鉴 外→内 교정·경맥혈 귀속 설명, 남은 이문 미해결 → 75 유지(점수 불변)</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>通考 L1037, L1055</t>
+          <t>通考 L1037, L1055; 经络通鉴 21편 L77·L98, 1편 L783~785</t>
         </is>
       </c>
     </row>
